--- a/bemenet.xlsx
+++ b/bemenet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Support\hrszProgi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E7D402-C7E7-4B5D-8E58-AC481D32EBB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE536743-4131-4D81-85E5-ECD2422A2125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30480" yWindow="2220" windowWidth="25605" windowHeight="13260" xr2:uid="{B28BD38A-BBEE-4FD9-847D-39E71E75A561}"/>
+    <workbookView xWindow="30795" yWindow="2220" windowWidth="25605" windowHeight="13260" xr2:uid="{B28BD38A-BBEE-4FD9-847D-39E71E75A561}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>Varos</t>
   </si>
@@ -51,19 +51,19 @@
     <t>Alsó köz 2/A</t>
   </si>
   <si>
-    <t>Alsó Muskátli utca 2/A</t>
-  </si>
-  <si>
-    <t>Alsó Muskátli utca 6/A</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>13</t>
   </si>
   <si>
     <t>14</t>
+  </si>
+  <si>
+    <t>Gödöllő</t>
+  </si>
+  <si>
+    <t>Szarvas utca 9</t>
+  </si>
+  <si>
+    <t>120</t>
   </si>
 </sst>
 </file>
@@ -449,7 +449,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -460,7 +460,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -471,7 +471,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>
@@ -487,19 +487,14 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A7"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8"/>
